--- a/sheets/investing/options-wheel-strategy-log/options-wheel-strategy-log.xlsx
+++ b/sheets/investing/options-wheel-strategy-log/options-wheel-strategy-log.xlsx
@@ -396,7 +396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -416,8 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1830,7 +1829,7 @@
       <c r="P21" s="2"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="23" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="4">
@@ -2423,7 +2422,7 @@
         <v>255</v>
       </c>
       <c r="K2" s="6">
-        <f t="shared" ref="K2:K21" si="3">I2+J2</f>
+        <f t="shared" ref="K2:K5" si="3">I2+J2</f>
         <v>3889.9999999999995</v>
       </c>
       <c r="L2" s="3"/>
@@ -3172,7 +3171,7 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3242,13 +3241,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="15" width="14.42578125" style="16" customWidth="1"/>
+    <col min="1" max="15" width="14.42578125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>67</v>
       </c>
@@ -3295,271 +3294,267 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="14">
         <v>3</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="16">
         <f>'Trade Log'!J4</f>
         <v>185</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="17">
         <v>178</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="16">
         <f>'Trade Log'!J5+'Trade Log'!J6</f>
         <v>255</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="J2" s="18">
+      <c r="J2" s="17">
         <v>190</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="14">
         <v>100</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="16">
         <f>D2+H2+IF(AND(I2="Yes",F2&lt;&gt;"",K2&lt;&gt;""),(J2-F2)*K2,0)</f>
         <v>1640</v>
       </c>
-      <c r="M2" s="19">
+      <c r="M2" s="18">
         <f>IF('Trade Log'!C6="",'Trade Log'!$B$22-'Trade Log'!B4,'Trade Log'!C6-'Trade Log'!B4)</f>
         <v>102</v>
       </c>
-      <c r="N2" s="20">
+      <c r="N2" s="19">
         <f>IF(OR(M2="",M2=0),"",IF(E2="Yes",IF(F2*K2-D2&lt;=0,"",(L2/(F2*K2-D2))*(365/M2)),IF('Trade Log'!F4*'Trade Log'!H4*100=0,"",(L2/('Trade Log'!F4*'Trade Log'!H4*100))*(365/M2))))</f>
         <v>0.33316079767132517</v>
       </c>
-      <c r="O2" s="21" t="str">
+      <c r="O2" s="20" t="str">
         <f>IF('Trade Log'!C6="","Active","Complete")</f>
         <v>Complete</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="14">
         <v>6</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="16">
         <f>'Trade Log'!J7</f>
         <v>90</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="18">
+      <c r="F3" s="17"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="17">
         <v>0</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="18"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="17">
+      <c r="J3" s="17"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="16">
         <f>D3+H3+IF(AND(I3="Yes",F3&lt;&gt;"",K3&lt;&gt;""),(J3-F3)*K3,0)</f>
         <v>90</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="18">
         <f>IF('Trade Log'!C7="",'Trade Log'!$B$22-'Trade Log'!B7,'Trade Log'!C7-'Trade Log'!B7)</f>
         <v>43</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="19">
         <f>IF(OR(M3="",M3=0),"",IF(E3="Yes",IF(F3*K3-D3&lt;=0,"",(L3/(F3*K3-D3))*(365/M3)),IF('Trade Log'!F7*'Trade Log'!H7*100=0,"",(L3/('Trade Log'!F7*'Trade Log'!H7*100))*(365/M3))))</f>
         <v>6.5858059342421824E-2</v>
       </c>
-      <c r="O3" s="21" t="str">
+      <c r="O3" s="20" t="str">
         <f>IF('Trade Log'!C7="","Active","Complete")</f>
         <v>Complete</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="14">
         <v>10</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <f>'Trade Log'!J11</f>
         <v>320</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="17">
         <v>405</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="17">
+      <c r="H4" s="16">
         <f>'Trade Log'!J12+'Trade Log'!J13+'Trade Log'!J14</f>
         <v>500</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="17">
         <v>430</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="14">
         <v>100</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="16">
         <f>D4+H4+IF(AND(I4="Yes",F4&lt;&gt;"",K4&lt;&gt;""),(J4-F4)*K4,0)</f>
         <v>820</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="18">
         <f>IF('Trade Log'!C14="",'Trade Log'!$B$22-'Trade Log'!B11,'Trade Log'!C14-'Trade Log'!B11)</f>
         <v>152</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="19">
         <f>IF(OR(M4="",M4=0),"",IF(E4="Yes",IF(F4*K4-D4&lt;=0,"",(L4/(F4*K4-D4))*(365/M4)),IF('Trade Log'!F11*'Trade Log'!H11*100=0,"",(L4/('Trade Log'!F11*'Trade Log'!H11*100))*(365/M4))))</f>
         <v>4.9006444683136405E-2</v>
       </c>
-      <c r="O4" s="21" t="str">
+      <c r="O4" s="20" t="str">
         <f>IF('Trade Log'!C14="","Active","Complete")</f>
         <v>Active</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="14">
         <v>16</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <f>'Trade Log'!J17</f>
         <v>60</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="17">
         <v>18.5</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="17">
+      <c r="H5" s="16">
         <f>'Trade Log'!J18</f>
         <v>36</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="17">
         <v>19</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="14">
         <v>400</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="16">
         <f>D5+H5+IF(AND(I5="Yes",F5&lt;&gt;"",K5&lt;&gt;""),(J5-F5)*K5,0)</f>
         <v>296</v>
       </c>
-      <c r="M5" s="19">
+      <c r="M5" s="18">
         <f>IF('Trade Log'!C18="",'Trade Log'!$B$22-'Trade Log'!B17,'Trade Log'!C18-'Trade Log'!B17)</f>
         <v>67</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="19">
         <f>IF(OR(M5="",M5=0),"",IF(E5="Yes",IF(F5*K5-D5&lt;=0,"",(L5/(F5*K5-D5))*(365/M5)),IF('Trade Log'!F17*'Trade Log'!H17*100=0,"",(L5/('Trade Log'!F17*'Trade Log'!H17*100))*(365/M5))))</f>
         <v>0.21969173207531822</v>
       </c>
-      <c r="O5" s="21" t="str">
+      <c r="O5" s="20" t="str">
         <f>IF('Trade Log'!C18="","Active","Complete")</f>
         <v>Complete</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="14">
         <v>18</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <f>'Trade Log'!J19</f>
         <v>82</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>61</v>
       </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="18">
+      <c r="G6" s="14"/>
+      <c r="H6" s="17">
         <v>0</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="15">
+      <c r="J6" s="17"/>
+      <c r="K6" s="14">
         <v>200</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="16">
         <f>D6+H6+IF(AND(I6="Yes",F6&lt;&gt;"",K6&lt;&gt;""),(J6-F6)*K6,0)</f>
         <v>82</v>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="18">
         <f>IF('Trade Log'!C19="",'Trade Log'!$B$22-'Trade Log'!B19,'Trade Log'!C19-'Trade Log'!B19)</f>
         <v>11</v>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="19">
         <f>IF(OR(M6="",M6=0),"",IF(E6="Yes",IF(F6*K6-D6&lt;=0,"",(L6/(F6*K6-D6))*(365/M6)),IF('Trade Log'!F19*'Trade Log'!H19*100=0,"",(L6/('Trade Log'!F19*'Trade Log'!H19*100))*(365/M6))))</f>
         <v>0.2230253353204173</v>
       </c>
-      <c r="O6" s="21" t="str">
+      <c r="O6" s="20" t="str">
         <f>IF('Trade Log'!C19="","Active","Complete")</f>
         <v>Active</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="P8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="22" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
         <v>84</v>
       </c>
     </row>
